--- a/site/Bob-UKG-Ready-integration-Guide/headings.xlsx
+++ b/site/Bob-UKG-Ready-integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,29 +595,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+          <t>h_01KSMN6ATB89NBF25R51385CS0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSMN6ATB89NBF25R51385CS0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,41 +627,41 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Integration Features</t>
+          <t>Parameters</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>General Settings</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,183 +683,183 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Application Configurations</t>
+          <t>Employee Match Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+          <t>h_01KSMNN8EDRYW9BJJNYQBFNYWJ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSMNN8EDRYW9BJJNYQBFNYWJ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Worker Sync Settings</t>
+          <t>Bob Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KRGHYGXSHZGM7MVSB83V5APW</t>
+          <t>h_01KSMQH2ZTZ24NCC7BAP8NGFP0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGHYGXSHZGM7MVSB83V5APW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSMQH2ZTZ24NCC7BAP8NGFP0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>User Match Settings</t>
+          <t>Eligible Employees Filter</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>h_01KSMQV5M7HSX0NRVSGEBGX4KS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSMQV5M7HSX0NRVSGEBGX4KS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Source Settings</t>
+          <t>UKG Ready Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KRGC3NR44QDZHD20J29AB4N8</t>
+          <t>h_01KSMT1XJNPFSYP6GG1KJ4DBCJ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGC3NR44QDZHD20J29AB4N8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSMT1XJNPFSYP6GG1KJ4DBCJ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Provisioning Settings</t>
+          <t>Company Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
+          <t>h_01KSMT36GJHSNGP9GD0X0RM7XQ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSMT36GJHSNGP9GD0X0RM7XQ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Execution Settings</t>
+          <t>Employee Management</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
+          <t>h_01KSMT4J39HJN2DHX1PX6HV4YZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSMT4J39HJN2DHX1PX6HV4YZ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Worker Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>h_01KSMT595NF4PG9N6CSK08SZF4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSMT595NF4PG9N6CSK08SZF4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Source Filter</t>
+          <t>Application Configurations</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KMMWQQRF8166YPHRS870BX9H</t>
+          <t>h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMWQQRF8166YPHRS870BX9H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Worker Sync Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,63 +869,63 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>h_01KRGHYGXSHZGM7MVSB83V5APW</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGHYGXSHZGM7MVSB83V5APW</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>User Match Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Source Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KRGC3NR44QDZHD20J29AB4N8</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGC3NR44QDZHD20J29AB4N8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Provisioning Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Execution Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,120 +957,274 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KRGHYGXSD8NWDN7EKG9G42WZ</t>
+          <t>h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGHYGXSD8NWDN7EKG9G42WZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Success Notification Settings</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KRGHYGXSV2916CB2H9D2CMPX</t>
+          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGHYGXSV2916CB2H9D2CMPX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Source Filter</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KMMWQQRF8166YPHRS870BX9H</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMWQQRF8166YPHRS870BX9H</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Notification Settings</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Notification Report Settings</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Notification Template Settings</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01KRGHYGXSD8NWDN7EKG9G42WZ</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGHYGXSD8NWDN7EKG9G42WZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Success Notification Settings</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01KRGHYGXSV2916CB2H9D2CMPX</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGHYGXSV2916CB2H9D2CMPX</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Log Insights</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Bob-UKG-Ready-integration-Guide/headings.xlsx
+++ b/site/Bob-UKG-Ready-integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -837,51 +837,51 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Application Configurations</t>
+          <t>Creation Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+          <t>h_01KSS8ZN6RQYWP1JAH9ZT5BA9Y</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSS8ZN6RQYWP1JAH9ZT5BA9Y</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Worker Sync Settings</t>
+          <t>Termination Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KRGHYGXSHZGM7MVSB83V5APW</t>
+          <t>h_01KSS91JK7F0RYGZ731WJ38DM0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGHYGXSHZGM7MVSB83V5APW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSS91JK7F0RYGZ731WJ38DM0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>User Match Settings</t>
+          <t>Safeguard Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,107 +891,107 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>h_01KSSCSA87RD4QG860C6GTV56K</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSSCSA87RD4QG860C6GTV56K</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Source Settings</t>
+          <t>Contract Management</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KRGC3NR44QDZHD20J29AB4N8</t>
+          <t>h_01KSSFH5TSP0Q87P84TP3K3T12</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGC3NR44QDZHD20J29AB4N8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSSFH5TSP0Q87P84TP3K3T12</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Provisioning Settings</t>
+          <t>Application Configurations</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
+          <t>h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Execution Settings</t>
+          <t>Worker Sync Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
+          <t>h_01KRGHYGXSHZGM7MVSB83V5APW</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGHYGXSHZGM7MVSB83V5APW</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>User Match Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Source Filter</t>
+          <t>Source Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,63 +1001,63 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KMMWQQRF8166YPHRS870BX9H</t>
+          <t>h_01KRGC3NR44QDZHD20J29AB4N8</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMWQQRF8166YPHRS870BX9H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGC3NR44QDZHD20J29AB4N8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Provisioning Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Execution Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,19 +1067,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Source Filter</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,63 +1089,63 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>h_01KMMWQQRF8166YPHRS870BX9H</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMWQQRF8166YPHRS870BX9H</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KRGHYGXSD8NWDN7EKG9G42WZ</t>
+          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGHYGXSD8NWDN7EKG9G42WZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Success Notification Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KRGHYGXSV2916CB2H9D2CMPX</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGHYGXSV2916CB2H9D2CMPX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,76 +1155,164 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KRGHYGXSD8NWDN7EKG9G42WZ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGHYGXSD8NWDN7EKG9G42WZ</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Success Notification Settings</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01KRGHYGXSV2916CB2H9D2CMPX</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGHYGXSV2916CB2H9D2CMPX</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Log Insights</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Bob-UKG-Ready-integration-Guide/headings.xlsx
+++ b/site/Bob-UKG-Ready-integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -925,29 +925,29 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Application Configurations</t>
+          <t>Contract Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+          <t>h_01KT1NPPVS865ZHNBH5RWY6BPT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KT1NPPVS865ZHNBH5RWY6BPT</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Worker Sync Settings</t>
+          <t>Application Configurations</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,41 +957,41 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KRGHYGXSHZGM7MVSB83V5APW</t>
+          <t>h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGHYGXSHZGM7MVSB83V5APW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>User Match Settings</t>
+          <t>Worker Sync Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>h_01KRGHYGXSHZGM7MVSB83V5APW</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGHYGXSHZGM7MVSB83V5APW</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Source Settings</t>
+          <t>User Match Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,19 +1001,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KRGC3NR44QDZHD20J29AB4N8</t>
+          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGC3NR44QDZHD20J29AB4N8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Provisioning Settings</t>
+          <t>Source Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,19 +1023,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
+          <t>h_01KRGC3NR44QDZHD20J29AB4N8</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGC3NR44QDZHD20J29AB4N8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Execution Settings</t>
+          <t>Provisioning Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,85 +1045,85 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
+          <t>h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Execution Settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Source Filter</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KMMWQQRF8166YPHRS870BX9H</t>
+          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMWQQRF8166YPHRS870BX9H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Source Filter</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>h_01KMMWQQRF8166YPHRS870BX9H</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMWQQRF8166YPHRS870BX9H</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,19 +1133,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,41 +1155,41 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1199,19 +1199,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KRGHYGXSD8NWDN7EKG9G42WZ</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGHYGXSD8NWDN7EKG9G42WZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Success Notification Settings</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1221,98 +1221,120 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01KRGHYGXSV2916CB2H9D2CMPX</t>
+          <t>h_01KRGHYGXSD8NWDN7EKG9G42WZ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGHYGXSV2916CB2H9D2CMPX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGHYGXSD8NWDN7EKG9G42WZ</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Success Notification Settings</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KRGHYGXSV2916CB2H9D2CMPX</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGHYGXSV2916CB2H9D2CMPX</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Bob-UKG-Ready-integration-Guide/headings.xlsx
+++ b/site/Bob-UKG-Ready-integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,29 +705,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bob Settings</t>
+          <t>Sensitive Fields</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KSMQH2ZTZ24NCC7BAP8NGFP0</t>
+          <t>h_01KT6483R1YATTAQ1W88YTTB80</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSMQH2ZTZ24NCC7BAP8NGFP0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KT6483R1YATTAQ1W88YTTB80</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Eligible Employees Filter</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,41 +737,41 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KSMQV5M7HSX0NRVSGEBGX4KS</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSMQV5M7HSX0NRVSGEBGX4KS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UKG Ready Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KSMT1XJNPFSYP6GG1KJ4DBCJ</t>
+          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSMT1XJNPFSYP6GG1KJ4DBCJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Company Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,41 +781,41 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KSMT36GJHSNGP9GD0X0RM7XQ</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSMT36GJHSNGP9GD0X0RM7XQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Employee Management</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KSMT4J39HJN2DHX1PX6HV4YZ</t>
+          <t>h_01K9750G1WVCA080W3BF2A4RY4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSMT4J39HJN2DHX1PX6HV4YZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K9750G1WVCA080W3BF2A4RY4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Worker Settings</t>
+          <t>Success Execution</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KSMT595NF4PG9N6CSK08SZF4</t>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSMT595NF4PG9N6CSK08SZF4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Creation Settings</t>
+          <t>Failure Execution</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KSS8ZN6RQYWP1JAH9ZT5BA9Y</t>
+          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSS8ZN6RQYWP1JAH9ZT5BA9Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Termination Settings</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,107 +869,107 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KSS91JK7F0RYGZ731WJ38DM0</t>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSS91JK7F0RYGZ731WJ38DM0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Safeguard Settings</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KSSCSA87RD4QG860C6GTV56K</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSSCSA87RD4QG860C6GTV56K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Contract Management</t>
+          <t>Bob Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KSSFH5TSP0Q87P84TP3K3T12</t>
+          <t>h_01KSMQH2ZTZ24NCC7BAP8NGFP0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSSFH5TSP0Q87P84TP3K3T12</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSMQH2ZTZ24NCC7BAP8NGFP0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Contract Settings</t>
+          <t>Eligible Employees Filter</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KT1NPPVS865ZHNBH5RWY6BPT</t>
+          <t>h_01KSMQV5M7HSX0NRVSGEBGX4KS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KT1NPPVS865ZHNBH5RWY6BPT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSMQV5M7HSX0NRVSGEBGX4KS</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Application Configurations</t>
+          <t>UKG Ready Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+          <t>h_01KSMT1XJNPFSYP6GG1KJ4DBCJ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSMT1XJNPFSYP6GG1KJ4DBCJ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Worker Sync Settings</t>
+          <t>Company Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,41 +979,41 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KRGHYGXSHZGM7MVSB83V5APW</t>
+          <t>h_01KSMT36GJHSNGP9GD0X0RM7XQ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGHYGXSHZGM7MVSB83V5APW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSMT36GJHSNGP9GD0X0RM7XQ</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>User Match Settings</t>
+          <t>Employee Management</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>h_01KSMT4J39HJN2DHX1PX6HV4YZ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSMT4J39HJN2DHX1PX6HV4YZ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Source Settings</t>
+          <t>Worker Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,19 +1023,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KRGC3NR44QDZHD20J29AB4N8</t>
+          <t>h_01KSMT595NF4PG9N6CSK08SZF4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGC3NR44QDZHD20J29AB4N8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSMT595NF4PG9N6CSK08SZF4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Provisioning Settings</t>
+          <t>Creation Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,19 +1045,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
+          <t>h_01KSS8ZN6RQYWP1JAH9ZT5BA9Y</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSS8ZN6RQYWP1JAH9ZT5BA9Y</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Execution Settings</t>
+          <t>Termination Settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,85 +1067,85 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
+          <t>h_01KSS91JK7F0RYGZ731WJ38DM0</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSS91JK7F0RYGZ731WJ38DM0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Safeguard Settings</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>h_01KSSCSA87RD4QG860C6GTV56K</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSSCSA87RD4QG860C6GTV56K</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Source Filter</t>
+          <t>Contract Management</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KMMWQQRF8166YPHRS870BX9H</t>
+          <t>h_01KSSFH5TSP0Q87P84TP3K3T12</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMWQQRF8166YPHRS870BX9H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KSSFH5TSP0Q87P84TP3K3T12</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Contract Settings</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>h_01KT1NPPVS865ZHNBH5RWY6BPT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KT1NPPVS865ZHNBH5RWY6BPT</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Compensation Management</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,186 +1155,120 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KT65KYDTZ4T7R88763XDFJRE</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KT65KYDTZ4T7R88763XDFJRE</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Compensation Settings</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KT65KYDTJTRMH5F7W7RH25CD</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KT65KYDTJTRMH5F7W7RH25CD</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>h_01KT63V5KV39BPGRVPTYTM066X</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KT63V5KV39BPGRVPTYTM066X</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01KRGHYGXSD8NWDN7EKG9G42WZ</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGHYGXSD8NWDN7EKG9G42WZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Success Notification Settings</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01KRGHYGXSV2916CB2H9D2CMPX</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01KRGHYGXSV2916CB2H9D2CMPX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Schedule</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Execute Integration</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Bob-UKG-Ready-integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
